--- a/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
+++ b/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>10.42584681510925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>36.68938255310059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>12.18739533424377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>18.1683030128479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1683,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>7.838905096054077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>10.57402300834656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>20.73189687728882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>10.28948616981506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>19.61123466491699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1828,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>57.88331699371338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1857,7 +1857,7 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>6.555334329605103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>9.416518688201904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>36.84824156761169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>13.26589131355286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>8.1169114112854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>12.40368700027466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2031,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>7.815099477767944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>6.445440292358398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>22.40979409217834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>10.31323456764221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2147,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>8.773087978363037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>7.416972637176514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2205,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>22.79461646080017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>9.132171869277954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>8.326855182647705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>7.99424147605896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>13.97769474983215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>6.747230052947998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2379,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>14.84294652938843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>12.52686715126038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>5.318986654281616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>19.52246260643005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>8.197539567947388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>35.48379683494568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>16.51732468605042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>5.64997386932373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>5.187315225601196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2640,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>7.217504024505615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>14.07769393920898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2698,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>13.00898838043213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>5.63420033454895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>8.293677091598511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2785,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>12.07555913925171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>24.90105366706848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>14.14327311515808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2872,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>16.41411852836609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2901,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>12.07014489173889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2930,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>17.19539761543274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>15.32151293754578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>11.67975163459778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>17.20310640335083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>15.0399284362793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>24.26013875007629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>10.42330646514893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3133,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>18.1692054271698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3162,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>2.609488487243652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3191,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>4.28880500793457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3220,7 +3220,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>6.97928786277771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3249,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>6.41717267036438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3278,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>3.878717184066772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>18.33335137367249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>10.6829628944397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>47.47773289680481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3394,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>69.11588573455811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3423,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>4.876641511917114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>17.02935004234314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>4.919668436050415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3510,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>15.66082739830017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3539,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>15.83708477020264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3568,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>34.52896308898926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3597,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>10.21742510795593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3626,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>14.44903635978699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>3.369699478149414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3684,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>18.67006611824036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3713,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>17.60184359550476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>14.05162191390991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>17.6993236541748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>7.602716445922852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>56.35796070098877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>8.232927799224854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3887,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>3.891856670379639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>22.76907587051392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>14.76159977912903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3974,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>17.35513877868652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>52.22659683227539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>15.87143635749817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>39.93126368522644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4090,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>34.38296008110046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4119,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>5.689532041549683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4148,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>7.865803718566895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4177,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>5.5882248878479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4206,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>12.91085815429688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>9.819501876831055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -4264,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>7.026498079299927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>32.73830389976501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -4322,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>4.655006408691406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4351,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>4.810722589492798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>3.164260625839233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -4409,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>6.779417276382446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>19.54239702224731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -4467,7 +4467,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>14.22370409965515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>23.66084933280945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -4525,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="I104">
-        <v>9.460651397705078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -4554,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>16.27564740180969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>7.458191633224487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -4612,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>139.8931748867035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>6.152080059051514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>23.41040778160095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>3.633209466934204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>19.37712025642395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4757,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>5.985708236694336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="I113">
-        <v>6.340633630752563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>56.5386323928833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4844,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>7.381253480911255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4873,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="I116">
-        <v>3.652372598648071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4902,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>7.220232725143433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>14.30617666244507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4960,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>17.01199841499329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>7.729046106338501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5018,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>91.48970103263855</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
+++ b/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="194">
   <si>
     <t>id</t>
   </si>
@@ -1149,6 +1149,28 @@
 In the back view (image 3), the backrest is visible. In the front view (image 1), the backrest is not visible. Therefore, if we turn right and move forward, we will be moving toward the back view (image 3), which means we will get closer to the backrest.
 ### Final Answer
 &lt;answer&gt;B. Yes&lt;/answer&gt;</t>
+  </si>
+  <si>
+    <t>To determine what is to the left of the yellow jar from the viewpoint presented in image 1, we must first understand the spatial configuration of the objects in the scene as captured in the four images. The question specifies that image 1 is the front view, and we need to identify what is to the left of the jar from this perspective.
+### Step 1: Understand the Camera Positions and Viewpoint Orientation
+The four images correspond to different camera viewpoints:
+- Image 1: Front view (azimuth = 0°, elevation = 0°)
+- Image 2: Left view (azimuth = -90°, elevation = 0°)
+- Image 3: Back view (azimuth = 180°, elevation = 0°)
+- Image 4: Right view (azimuth = 90°, elevation = 0°)
+From the front view (image 1), the “left” of the jar corresponds to the direction of the left view (image 2) in the 3D space. This is because in a typical 3D coordinate system, if the camera is facing forward (front view), then the left side of the scene is toward the left view camera.
+### Step 2: Analyze Image 1 (Front View)
+In image 1, the yellow jar is centered, and to its left, there is a dark-colored object that appears to be a small figurine or decorative item. The background consists of a plain wall. There are no visible display shelves or windows in this image.
+### Step 3: Analyze Image 2 (Left View)
+In image 2, the camera is positioned to the left of the jar. In this view, the jar is still centered, and to its left (from the viewer’s perspective), there is a large window with a blue light emanating from behind it. To the right of the jar (from the viewer’s perspective), there is a black chair.
+### Step 4: Analyze Image 3 (Back View)
+In image 3, the jar is centered, and behind it, there are display shelves with various items on them. The wall behind the jar is a plain beige color.
+### Step 5: Analyze Image 4 (Right View)
+In image 4, the jar is centered, and to its right, there is a black chair. To its left, there is a display shelf with various items on it.
+### Step 6: Determine the Answer
+From the front view (image 1), the left side of the jar corresponds to the left view (image 2). In image 2, the left side of the jar (from the viewer’s perspective) is the window with the blue light. Therefore, the correct answer is C. Window.
+### Final Answer
+&lt;answer&gt;C&lt;/answer&gt;</t>
   </si>
 </sst>
 </file>
@@ -5006,19 +5028,19 @@
         <v>136</v>
       </c>
       <c r="E121" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="F121" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G121" t="s">
         <v>136</v>
       </c>
       <c r="H121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>4.505929470062256</v>
       </c>
     </row>
   </sheetData>
